--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinsu99/Desktop/RENE/flaky_tests_AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582CD7C-739E-CC41-A9A4-C34A0F6188CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9765DB-B122-B44A-9E72-CABCF1D9DC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="23100" windowWidth="22820" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="22300" windowWidth="27040" windowHeight="16860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="70-30 normal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="745">
   <si>
     <t>classifier</t>
   </si>
@@ -2627,6 +2627,9 @@
   <si>
     <t>[[242  11]
  [ 14 305]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{'Flaky': {'precision': 0.20833333333333334, 'recall': 0.04424778761061947, 'f1-score': 0.072992700729927, 'support': 113.0}, 'NonFlaky': {'precision': 0.41935483870967744, 'recall': 0.8041237113402062, 'f1-score': 0.5512367491166078, 'support': 97.0}, 'accuracy': 0.3952380952380952, 'macro avg': {'precision': 0.3138440860215054, 'recall': 0.4241857494754128, 'f1-score': 0.3121147249232674, 'support': 210.0}, </t>
   </si>
 </sst>
 </file>
@@ -4805,10 +4808,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5749225-216B-C447-84F8-7889D13B2B48}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="1" customWidth="1"/>
+    <col min="6" max="6" width="0.1640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="2.5" customWidth="1"/>
+    <col min="8" max="8" width="2" customWidth="1"/>
+    <col min="9" max="9" width="187" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4831,7 +4844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>123</v>
       </c>
@@ -4856,8 +4869,12 @@
       <c r="H2">
         <v>0.91156785918135108</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="str">
+        <f>MID(F2,300,300)</f>
+        <v>': 0.9552511867088608, 'recall': 0.9563172958975058, 'f1-score': 0.9557570038519252, 'support': 572.0}, 'weighted avg': {'precision': 0.9563979582521908, 'recall': 0.9562937062937062, 'f1-score': 0.9563192635528388, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" t="s">
         <v>8</v>
@@ -4880,8 +4897,12 @@
       <c r="H3">
         <v>0.86273877165168966</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I66" si="0">MID(F3,300,300)</f>
+        <v>precision': 0.9300049248953459, 'recall': 0.9327381763663622, 'f1-score': 0.9311343325049779, 'support': 572.0}, 'weighted avg': {'precision': 0.9324981531642451, 'recall': 0.9318181818181818, 'f1-score': 0.9319261580255299, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" t="s">
         <v>9</v>
@@ -4904,8 +4925,12 @@
       <c r="H4">
         <v>0.90448877783764892</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>: 0.9517157832278481, 'recall': 0.9527736131934033, 'f1-score': 0.9522175641600792, 'support': 572.0}, 'weighted avg': {'precision': 0.9529053447541382, 'recall': 0.9527972027972028, 'f1-score': 0.952824804637066, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>10</v>
@@ -4928,8 +4953,12 @@
       <c r="H5">
         <v>0.91854561649887634</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>recision': 0.9607337024290489, 'recall': 0.9578165462723184, 'f1-score': 0.9591244504512901, 'support': 572.0}, 'weighted avg': {'precision': 0.9599553210020068, 'recall': 0.9597902097902098, 'f1-score': 0.959726369853601, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
         <v>11</v>
@@ -4952,8 +4981,12 @@
       <c r="H6">
         <v>0.14036360657033781</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> {'precision': 0.6996590453269154, 'recall': 0.5246694834400981, 'f1-score': 0.36271276185013185, 'support': 572.0}, 'weighted avg': {'precision': 0.727903514455861, 'recall': 0.47027972027972026, 'f1-score': 0.33250246714224746, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>12</v>
@@ -4976,8 +5009,12 @@
       <c r="H7">
         <v>0.90426709332998678</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.95313122262047, 'recall': 0.9511380673299714, 'f1-score': 0.952058557845429, 'support': 572.0}, 'weighted avg': {'precision': 0.9528411527739485, 'recall': 0.9527972027972028, 'f1-score': 0.9527451855470781, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" t="s">
         <v>13</v>
@@ -5000,8 +5037,12 @@
       <c r="H8">
         <v>0.91504269960507689</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>recision': 0.9592086375834739, 'recall': 0.9558402616873382, 'f1-score': 0.9573277630646426, 'support': 572.0}, 'weighted avg': {'precision': 0.9582696028305464, 'recall': 0.958041958041958, 'f1-score': 0.9579647477741403, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" t="s">
         <v>14</v>
@@ -5024,8 +5065,12 @@
       <c r="H9">
         <v>0.58379993140149056</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.7937751004016065, 'recall': 0.7900367997819273, 'f1-score': 0.7914769912414354, 'support': 572.0}, 'weighted avg': {'precision': 0.794979919678715, 'recall': 0.7954545454545454, 'f1-score': 0.7948000112169451, 'support': 572.0}}</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>124</v>
       </c>
@@ -5050,8 +5095,12 @@
       <c r="H10">
         <v>0.8240856434303292</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>'recall': 0.9210526315789473, 'f1-score': 0.9035714285714285, 'support': 63.0}, 'weighted avg': {'precision': 0.923195084485407, 'recall': 0.9047619047619048, 'f1-score': 0.90578231292517, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" t="s">
         <v>8</v>
@@ -5074,8 +5123,12 @@
       <c r="H11">
         <v>0.76988964013890715</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>5363825363826, 'recall': 0.8873684210526316, 'f1-score': 0.8847058823529412, 'support': 63.0}, 'weighted avg': {'precision': 0.8900438900438901, 'recall': 0.8888888888888888, 'f1-score': 0.8892374727668845, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" t="s">
         <v>9</v>
@@ -5098,8 +5151,12 @@
       <c r="H12">
         <v>0.93368421052631578</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" t="str">
+        <f t="shared" si="0"/>
+        <v>66842105263158, 'f1-score': 0.966842105263158, 'support': 63.0}, 'weighted avg': {'precision': 0.9682539682539683, 'recall': 0.9682539682539683, 'f1-score': 0.9682539682539683, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" t="s">
         <v>10</v>
@@ -5122,8 +5179,12 @@
       <c r="H13">
         <v>0.96759227870718623</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" t="str">
+        <f t="shared" si="0"/>
+        <v>'recall': 0.986842105263158, 'f1-score': 0.9835294117647058, 'support': 63.0}, 'weighted avg': {'precision': 0.9847374847374848, 'recall': 0.9841269841269841, 'f1-score': 0.9841767818238406, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" t="s">
         <v>11</v>
@@ -5146,8 +5207,12 @@
       <c r="H14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" t="str">
+        <f t="shared" si="0"/>
+        <v>840909090909091, 'support': 63.0}, 'weighted avg': {'precision': 0.15747039556563366, 'recall': 0.3968253968253968, 'f1-score': 0.22546897546897549, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" t="s">
         <v>12</v>
@@ -5170,8 +5235,12 @@
       <c r="H15">
         <v>0.63628476297577774</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" t="str">
+        <f t="shared" si="0"/>
+        <v>recall': 0.8157894736842105, 'f1-score': 0.7777217741935485, 'support': 63.0}, 'weighted avg': {'precision': 0.8575498575498575, 'recall': 0.7777777777777778, 'f1-score': 0.7769937275985663, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" t="s">
         <v>13</v>
@@ -5194,8 +5263,12 @@
       <c r="H16">
         <v>0.93658581158169396</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" t="str">
+        <f t="shared" si="0"/>
+        <v>ecall': 0.9736842105263157, 'f1-score': 0.9672557172557172, 'support': 63.0}, 'weighted avg': {'precision': 0.9706055261610818, 'recall': 0.9682539682539683, 'f1-score': 0.9684354684354685, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" t="s">
         <v>14</v>
@@ -5218,8 +5291,12 @@
       <c r="H17">
         <v>0.90169139918442653</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v>0249480249481, 'recall': 0.9536842105263157, 'f1-score': 0.9505882352941175, 'support': 63.0}, 'weighted avg': {'precision': 0.9531729531729531, 'recall': 0.9523809523809523, 'f1-score': 0.9525303454715218, 'support': 63.0}}</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>125</v>
       </c>
@@ -5244,8 +5321,12 @@
       <c r="H18">
         <v>0.84515425472851657</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 'f1-score': 0.9163763066202091, 'support': 24.0}, 'weighted avg': {'precision': 0.9603174603174603, 'recall': 0.9583333333333334, 'f1-score': 0.9558652729384436, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" t="s">
         <v>8</v>
@@ -5268,8 +5349,12 @@
       <c r="H19">
         <v>0.84515425472851657</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 'f1-score': 0.9163763066202091, 'support': 24.0}, 'weighted avg': {'precision': 0.9603174603174603, 'recall': 0.9583333333333334, 'f1-score': 0.9558652729384436, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" t="s">
         <v>9</v>
@@ -5292,8 +5377,12 @@
       <c r="H20">
         <v>0.87177978870813466</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v>6, 'support': 24.0}, 'weighted avg': {'precision': 0.9666666666666667, 'recall': 0.9583333333333334, 'f1-score': 0.9601139601139601, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" t="s">
         <v>10</v>
@@ -5316,8 +5405,12 @@
       <c r="H21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" t="str">
+        <f t="shared" si="0"/>
+        <v>l': 1.0, 'f1-score': 1.0, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" t="s">
         <v>11</v>
@@ -5340,8 +5433,12 @@
       <c r="H22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" t="str">
+        <f t="shared" si="0"/>
+        <v>454545454545453, 'support': 24.0}, 'weighted avg': {'precision': 0.6944444444444445, 'recall': 0.8333333333333334, 'f1-score': 0.7575757575757575, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" t="s">
         <v>12</v>
@@ -5364,8 +5461,12 @@
       <c r="H23">
         <v>0.46625240412015689</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v>7674, 'support': 24.0}, 'weighted avg': {'precision': 0.8913043478260869, 'recall': 0.875, 'f1-score': 0.8418604651162792, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" t="s">
         <v>13</v>
@@ -5388,8 +5489,12 @@
       <c r="H24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v>l': 1.0, 'f1-score': 1.0, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" t="s">
         <v>14</v>
@@ -5412,8 +5517,12 @@
       <c r="H25">
         <v>0.84515425472851657</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 'f1-score': 0.9163763066202091, 'support': 24.0}, 'weighted avg': {'precision': 0.9603174603174603, 'recall': 0.9583333333333334, 'f1-score': 0.9558652729384436, 'support': 24.0}}</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>126</v>
       </c>
@@ -5438,8 +5547,12 @@
       <c r="H26">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" t="str">
+        <f t="shared" si="0"/>
+        <v>889795918367347, 'support': 27.0}, 'weighted avg': {'precision': 0.9753086419753086, 'recall': 0.9629629629629629, 'f1-score': 0.9662887377173092, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" t="s">
         <v>8</v>
@@ -5462,8 +5575,12 @@
       <c r="H27">
         <v>0.52915026221291817</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27" t="str">
+        <f t="shared" si="0"/>
+        <v>'f1-score': 0.7065217391304348, 'support': 27.0}, 'weighted avg': {'precision': 0.9506172839506173, 'recall': 0.8518518518518519, 'f1-score': 0.8824476650563609, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" t="s">
         <v>9</v>
@@ -5486,8 +5603,12 @@
       <c r="H28">
         <v>0.69337524528153638</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" t="str">
+        <f t="shared" si="0"/>
+        <v>'f1-score': 0.8235294117647058, 'support': 27.0}, 'weighted avg': {'precision': 0.9643874643874645, 'recall': 0.9629629629629629, 'f1-score': 0.9571532316630355, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" t="s">
         <v>10</v>
@@ -5510,8 +5631,12 @@
       <c r="H29">
         <v>0.67823299831252681</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29" t="str">
+        <f t="shared" si="0"/>
+        <v>': 27.0}, 'weighted avg': {'precision': 0.9629629629629629, 'recall': 0.9259259259259259, 'f1-score': 0.9367283950617284, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" t="s">
         <v>11</v>
@@ -5534,8 +5659,12 @@
       <c r="H30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 0.06896551724137931, 'support': 27.0}, 'weighted avg': {'precision': 0.0054869684499314125, 'recall': 0.07407407407407407, 'f1-score': 0.010217113665389528, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" t="s">
         <v>12</v>
@@ -5558,8 +5687,12 @@
       <c r="H31">
         <v>0.69337524528153638</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31" t="str">
+        <f t="shared" si="0"/>
+        <v>'f1-score': 0.8235294117647058, 'support': 27.0}, 'weighted avg': {'precision': 0.9643874643874645, 'recall': 0.9629629629629629, 'f1-score': 0.9571532316630355, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
       <c r="B32" t="s">
         <v>13</v>
@@ -5582,8 +5715,12 @@
       <c r="H32">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32" t="str">
+        <f t="shared" si="0"/>
+        <v>889795918367347, 'support': 27.0}, 'weighted avg': {'precision': 0.9753086419753086, 'recall': 0.9629629629629629, 'f1-score': 0.9662887377173092, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" t="s">
         <v>14</v>
@@ -5606,8 +5743,12 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33" t="str">
+        <f t="shared" si="0"/>
+        <v>889795918367347, 'support': 27.0}, 'weighted avg': {'precision': 0.9753086419753086, 'recall': 0.9629629629629629, 'f1-score': 0.9662887377173092, 'support': 27.0}}</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>127</v>
       </c>
@@ -5632,8 +5773,12 @@
       <c r="H34">
         <v>0.90263570144627781</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34" t="str">
+        <f t="shared" si="0"/>
+        <v>recision': 0.9518183213134878, 'recall': 0.9508179344945766, 'f1-score': 0.9513063572910772, 'support': 590.0}, 'weighted avg': {'precision': 0.9525122040660281, 'recall': 0.9525423728813559, 'f1-score': 0.9525160746773075, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" t="s">
         <v>8</v>
@@ -5656,8 +5801,12 @@
       <c r="H35">
         <v>0.8824467792443067</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9398887913374305, 'recall': 0.9425620370043223, 'f1-score': 0.9411219122757584, 'support': 590.0}, 'weighted avg': {'precision': 0.9427454948587075, 'recall': 0.9423728813559322, 'f1-score': 0.9424601582685025, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
       <c r="B36" t="s">
         <v>9</v>
@@ -5680,8 +5829,12 @@
       <c r="H36">
         <v>0.88579051323454372</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I36" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9417650918635171, 'recall': 0.9440283126641463, 'f1-score': 0.9428245886571267, 'support': 590.0}, 'weighted avg': {'precision': 0.9443486142622003, 'recall': 0.9440677966101695, 'f1-score': 0.9441392453431031, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" t="s">
         <v>10</v>
@@ -5704,8 +5857,15 @@
       <c r="H37">
         <v>0.90609036033544021</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9538074305161657, 'recall': 0.9522842101544007, 'f1-score': 0.9530192435301924, 'support': 590.0}, 'weighted avg': {'precision': 0.9542109703221588, 'recall': 0.9542372881355933, 'f1-score': 0.9541988235691069, 'support': 590.0}}</v>
+      </c>
+      <c r="J37" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" t="s">
         <v>11</v>
@@ -5728,8 +5888,12 @@
       <c r="H38">
         <v>0.117782168192991</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38" t="str">
+        <f t="shared" si="0"/>
+        <v>: 0.5161290322580645, 'f1-score': 0.3319746376811594, 'support': 590.0}, 'weighted avg': {'precision': 0.7594625450074647, 'recall': 0.4406779661016949, 'f1-score': 0.28995486366986, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" t="s">
         <v>12</v>
@@ -5752,8 +5916,12 @@
       <c r="H39">
         <v>0.87831960182443547</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39" t="str">
+        <f t="shared" si="0"/>
+        <v>recision': 0.9421194614209321, 'recall': 0.9362199531262881, 'f1-score': 0.938813183166366, 'support': 590.0}, 'weighted avg': {'precision': 0.940956149408916, 'recall': 0.940677966101695, 'f1-score': 0.9404788145260774, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
       <c r="B40" t="s">
         <v>13</v>
@@ -5776,8 +5944,12 @@
       <c r="H40">
         <v>0.90609036033544021</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9538074305161657, 'recall': 0.9522842101544007, 'f1-score': 0.9530192435301924, 'support': 590.0}, 'weighted avg': {'precision': 0.9542109703221588, 'recall': 0.9542372881355933, 'f1-score': 0.9541988235691069, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="B41" t="s">
         <v>14</v>
@@ -5800,8 +5972,12 @@
       <c r="H41">
         <v>0.48504512159308688</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.7455917874396136, 'recall': 0.7394916911045943, 'f1-score': 0.7417051096107856, 'support': 590.0}, 'weighted avg': {'precision': 0.7493111848030788, 'recall': 0.7508474576271187, 'f1-score': 0.7492825512099085, 'support': 590.0}}</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>531</v>
       </c>
@@ -5826,8 +6002,12 @@
       <c r="H42">
         <v>0.87595073196513618</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42" t="str">
+        <f t="shared" si="0"/>
+        <v>ecision': 0.9362828170579247, 'recall': 0.9396744811109452, 'f1-score': 0.9373425027231788, 'support': 658.0}, 'weighted avg': {'precision': 0.9391850691859854, 'recall': 0.9376899696048632, 'f1-score': 0.9378105193393252, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
       <c r="B43" t="s">
         <v>8</v>
@@ -5850,8 +6030,12 @@
       <c r="H43">
         <v>0.86214551511848336</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I43" t="str">
+        <f t="shared" si="0"/>
+        <v>ecision': 0.9304605563155495, 'recall': 0.9316858294758847, 'f1-score': 0.9310180946456903, 'support': 658.0}, 'weighted avg': {'precision': 0.9318163683088279, 'recall': 0.9316109422492401, 'f1-score': 0.931659536315105, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" t="s">
         <v>9</v>
@@ -5874,8 +6058,12 @@
       <c r="H44">
         <v>0.84960049434568896</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44" t="str">
+        <f t="shared" si="0"/>
+        <v>cision': 0.924671460682541, 'recall': 0.9249290727191279, 'f1-score': 0.9247980706210539, 'support': 658.0}, 'weighted avg': {'precision': 0.9255588040877132, 'recall': 0.925531914893617, 'f1-score': 0.9255432048055026, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
       <c r="B45" t="s">
         <v>10</v>
@@ -5898,8 +6086,16 @@
       <c r="H45">
         <v>0.89893804466803129</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9488306950687252, 'recall': 0.9501082574286994, 'f1-score': 0.9494132694068396, 'support': 658.0}, 'weighted avg': {'precision': 0.9500296902531423, 'recall': 0.9498480243161094, 'f1-score': 0.9498836599644104, 'support': 658.0}}</v>
+      </c>
+      <c r="O45">
+        <f>LEN(J37)</f>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
       <c r="B46" t="s">
         <v>11</v>
@@ -5922,8 +6118,12 @@
       <c r="H46">
         <v>0.14275260677727891</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46" t="str">
+        <f t="shared" si="0"/>
+        <v>5763, 'recall': 0.5220994475138121, 'f1-score': 0.3578930743109847, 'support': 658.0}, 'weighted avg': {'precision': 0.7575585414121903, 'recall': 0.47416413373860183, 'f1-score': 0.3304863245887607, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="5"/>
       <c r="B47" t="s">
         <v>12</v>
@@ -5946,8 +6146,12 @@
       <c r="H47">
         <v>0.8772759360300596</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I47" t="str">
+        <f t="shared" si="0"/>
+        <v>recision': 0.9383762117822521, 'recall': 0.9388998805435269, 'f1-score': 0.9386291353050356, 'support': 658.0}, 'weighted avg': {'precision': 0.9392635015832218, 'recall': 0.939209726443769, 'f1-score': 0.9392278699168545, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="5"/>
       <c r="B48" t="s">
         <v>13</v>
@@ -5970,8 +6174,12 @@
       <c r="H48">
         <v>0.9017035175026723</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9511381475667191, 'recall': 0.9505655517395849, 'f1-score': 0.9508427884390905, 'support': 658.0}, 'weighted avg': {'precision': 0.9513546592356841, 'recall': 0.9513677811550152, 'f1-score': 0.951352340192782, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="B49" t="s">
         <v>14</v>
@@ -5994,8 +6202,12 @@
       <c r="H49">
         <v>0.59341675232762225</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49" t="str">
+        <f t="shared" si="0"/>
+        <v>ecision': 0.8004209720627631, 'recall': 0.7930416604449754, 'f1-score': 0.7952127659574468, 'support': 658.0}, 'weighted avg': {'precision': 0.799864367663669, 'recall': 0.7993920972644377, 'f1-score': 0.7981471900666106, 'support': 658.0}}</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>129</v>
       </c>
@@ -6020,8 +6232,12 @@
       <c r="H50">
         <v>0.8096371797550308</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50" t="str">
+        <f t="shared" si="0"/>
+        <v>8281101614435, 'recall': 0.9078313253012048, 'f1-score': 0.9045911047345767, 'support': 133.0}, 'weighted avg': {'precision': 0.9108704810459197, 'recall': 0.9097744360902256, 'f1-score': 0.9101088445647836, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="5"/>
       <c r="B51" t="s">
         <v>8</v>
@@ -6044,8 +6260,12 @@
       <c r="H51">
         <v>0.73133272496311108</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51" t="str">
+        <f t="shared" si="0"/>
+        <v>59360730593608, 'recall': 0.8756626506024097, 'f1-score': 0.8604895104895105, 'support': 133.0}, 'weighted avg': {'precision': 0.8780856250214577, 'recall': 0.8646616541353384, 'f1-score': 0.8664756296335244, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="5"/>
       <c r="B52" t="s">
         <v>9</v>
@@ -6068,8 +6288,12 @@
       <c r="H52">
         <v>0.7957954173831544</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52" t="str">
+        <f t="shared" si="0"/>
+        <v>3496999454447, 'recall': 0.8739759036144579, 'f1-score': 0.8902431282930237, 'support': 133.0}, 'weighted avg': {'precision': 0.9106932634368246, 'recall': 0.9022556390977443, 'f1-score': 0.8992525113965643, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="5"/>
       <c r="B53" t="s">
         <v>10</v>
@@ -6092,8 +6316,12 @@
       <c r="H53">
         <v>0.83891248378201555</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I53" t="str">
+        <f t="shared" si="0"/>
+        <v>0392156862746, 'recall': 0.9159036144578313, 'f1-score': 0.9192176870748299, 'support': 133.0}, 'weighted avg': {'precision': 0.9246203744655757, 'recall': 0.924812030075188, 'f1-score': 0.9244923533323103, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="5"/>
       <c r="B54" t="s">
         <v>11</v>
@@ -6116,8 +6344,12 @@
       <c r="H54">
         <v>6.7555232091870518E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54" t="str">
+        <f t="shared" si="0"/>
+        <v>94, 'recall': 0.5060240963855421, 'f1-score': 0.2866300366300366, 'support': 133.0}, 'weighted avg': {'precision': 0.7664616085668717, 'recall': 0.38345864661654133, 'f1-score': 0.22141893194524773, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" t="s">
         <v>12</v>
@@ -6140,8 +6372,12 @@
       <c r="H55">
         <v>0.7616972245635798</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I55" t="str">
+        <f t="shared" si="0"/>
+        <v>52100381887616, 'recall': 0.8579518072289156, 'f1-score': 0.8733574557227195, 'support': 133.0}, 'weighted avg': {'precision': 0.8944148423431738, 'recall': 0.8872180451127819, 'f1-score': 0.8837528977652663, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" t="s">
         <v>13</v>
@@ -6164,8 +6400,12 @@
       <c r="H56">
         <v>0.85646334970271332</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I56" t="str">
+        <f t="shared" si="0"/>
+        <v>65901482544237, 'recall': 0.9298795180722892, 'f1-score': 0.9281728172817282, 'support': 133.0}, 'weighted avg': {'precision': 0.9327011934427174, 'recall': 0.9323308270676691, 'f1-score': 0.9324607648734798, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="B57" t="s">
         <v>14</v>
@@ -6188,8 +6428,12 @@
       <c r="H57">
         <v>0.65859387535988767</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 'recall': 0.8356626506024096, 'f1-score': 0.8274764150943397, 'support': 133.0}, 'weighted avg': {'precision': 0.8411776193731081, 'recall': 0.8345864661654135, 'f1-score': 0.836166477514541, 'support': 133.0}}</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>130</v>
       </c>
@@ -6214,8 +6458,12 @@
       <c r="H58">
         <v>0.87806002459707966</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I58" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9374649929162137, 'recall': 0.9406006304961009, 'f1-score': 0.9389030317056237, 'support': 704.0}, 'weighted avg': {'precision': 0.9408010556788604, 'recall': 0.9403409090909091, 'f1-score': 0.9404474185268561, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" t="s">
         <v>8</v>
@@ -6238,8 +6486,12 @@
       <c r="H59">
         <v>0.82798867144229982</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9134134134134134, 'recall': 0.9145760743321719, 'f1-score': 0.9139768912305555, 'support': 704.0}, 'weighted avg': {'precision': 0.916344805549351, 'recall': 0.9161931818181818, 'f1-score': 0.9162520213913047, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" t="s">
         <v>9</v>
@@ -6262,8 +6514,12 @@
       <c r="H60">
         <v>0.8092244474571777</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I60" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 0.9022366522366523, 'recall': 0.907001825120292, 'f1-score': 0.9042397962127895, 'support': 704.0}, 'weighted avg': {'precision': 0.9075269742883378, 'recall': 0.90625, 'f1-score': 0.9065259103237348, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" t="s">
         <v>10</v>
@@ -6286,8 +6542,12 @@
       <c r="H61">
         <v>0.8889409858055366</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61" t="str">
+        <f t="shared" si="0"/>
+        <v>recision': 0.9449062375315866, 'recall': 0.944035175045628, 'f1-score': 0.9444624365777302, 'support': 704.0}, 'weighted avg': {'precision': 0.9459855109480224, 'recall': 0.9460227272727273, 'f1-score': 0.9459962816677273, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" t="s">
         <v>11</v>
@@ -6310,8 +6570,12 @@
       <c r="H62">
         <v>3.1937732152392893E-2</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I62" t="str">
+        <f t="shared" si="0"/>
+        <v>27881, 'recall': 0.501219512195122, 'f1-score': 0.2973177439862166, 'support': 704.0}, 'weighted avg': {'precision': 0.7570355942066468, 'recall': 0.4190340909090909, 'f1-score': 0.2491297022010513, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" t="s">
         <v>12</v>
@@ -6334,8 +6598,12 @@
       <c r="H63">
         <v>0.88298377919218141</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I63" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9433198380566802, 'recall': 0.9396714783474365, 'f1-score': 0.9413626520073297, 'support': 704.0}, 'weighted avg': {'precision': 0.9431985478636197, 'recall': 0.9431818181818182, 'f1-score': 0.9430644526221738, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" t="s">
         <v>13</v>
@@ -6358,8 +6626,12 @@
       <c r="H64">
         <v>0.89178783113628868</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.9470171342810689, 'recall': 0.9447735191637631, 'f1-score': 0.9458433390508862, 'support': 704.0}, 'weighted avg': {'precision': 0.9474093685215856, 'recall': 0.9474431818181818, 'f1-score': 0.9473770726129217, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="B65" t="s">
         <v>14</v>
@@ -6381,6 +6653,370 @@
       </c>
       <c r="H65">
         <v>0.55181668170214682</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="0"/>
+        <v>precision': 0.7768990382606806, 'recall': 0.7749211879873901, 'f1-score': 0.7758274417413998, 'support': 704.0}, 'weighted avg': {'precision': 0.7820489174070943, 'recall': 0.7826704545454546, 'f1-score': 0.7822810147923782, 'support': 704.0}}</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I67" t="str">
+        <f t="shared" ref="I67:I115" si="1">MID(F67,300,300)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I68" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I69" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I70" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I71" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I72" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I73" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I74" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I75" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I76" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I77" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I78" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I79" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I80" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I81" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I82" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I83" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I84" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I85" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I86" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I87" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I88" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I89" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I90" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I92" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I93" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I94" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I95" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I96" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I97" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I98" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I99" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I100" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I101" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I102" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I103" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I104" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I105" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I106" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I107" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I108" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I109" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I110" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I112" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I113" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I114" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I115" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I116" t="str">
+        <f t="shared" ref="I67:I125" si="2">MID(F116,300,200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I117" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I118" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I119" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I120" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I121" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I122" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I123" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I124" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I125" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -17269,16 +17905,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A50:A57"/>
     <mergeCell ref="A58:A65"/>
     <mergeCell ref="A98:A105"/>
     <mergeCell ref="A106:A113"/>
     <mergeCell ref="A114:A121"/>
-    <mergeCell ref="A122:A129"/>
-    <mergeCell ref="A66:A73"/>
-    <mergeCell ref="A74:A81"/>
-    <mergeCell ref="A82:A89"/>
-    <mergeCell ref="A90:A97"/>
     <mergeCell ref="A130:A137"/>
     <mergeCell ref="A138:A145"/>
     <mergeCell ref="A146:A153"/>
@@ -17289,6 +17919,12 @@
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="A34:A41"/>
     <mergeCell ref="A42:A49"/>
+    <mergeCell ref="A122:A129"/>
+    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="A82:A89"/>
+    <mergeCell ref="A90:A97"/>
+    <mergeCell ref="A50:A57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
